--- a/output/pdf_financials_xlsx/CGI.xlsx
+++ b/output/pdf_financials_xlsx/CGI.xlsx
@@ -2353,46 +2353,46 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>5.66</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>9.441000000000001</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.354</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>3.683</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>5.613</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>5.613</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>11.133</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>17.238</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>13.655</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>5.868</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>21.041</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>16.599</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>3.598</v>
       </c>
     </row>
     <row r="35">
@@ -2451,46 +2451,46 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>5.66</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>9.441000000000001</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.354</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>3.683</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>5.613</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>5.613</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>11.133</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>17.238</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>13.655</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>5.868</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>21.041</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>16.599</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>3.598</v>
       </c>
     </row>
     <row r="37">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -14588,7 +14588,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">

--- a/output/pdf_financials_xlsx/CGI.xlsx
+++ b/output/pdf_financials_xlsx/CGI.xlsx
@@ -5771,19 +5771,19 @@
         <v>0</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>-0.017</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0</v>
+        <v>-0.024</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0</v>
+        <v>0.082</v>
       </c>
       <c r="L101" s="3" t="n">
         <v>0</v>
@@ -6001,34 +6001,34 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0</v>
+        <v>-16.753</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0</v>
+        <v>24.966</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0</v>
+        <v>2.545</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>-2.603</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>2.518</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.051</v>
+        <v>0.251</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.016</v>
+        <v>0.022</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.089</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0.153</v>
+        <v>0.129</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0.034</v>
+        <v>0.116</v>
       </c>
       <c r="L106" s="3" t="n">
         <v>0.03</v>
@@ -31304,7 +31304,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr"/>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E289" t="inlineStr">
         <is>
           <t>-</t>
@@ -52446,7 +52450,11 @@
           <t>Net change in non-cash balances related to operations</t>
         </is>
       </c>
-      <c r="D541" t="inlineStr"/>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E541" s="5" t="n">
         <v>-16.753</v>
       </c>
